--- a/com.crm.VTiger/src/test/resources/TestData/VTigerTestData.xlsx
+++ b/com.crm.VTiger/src/test/resources/TestData/VTigerTestData.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Leads" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Contacts" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t xml:space="preserve">TC_ID</t>
   </si>
@@ -31,6 +32,72 @@
     <t xml:space="preserve">Last Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SoftSuave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. of Employees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LE_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qspider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spiddy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bangalore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karnataka</t>
+  </si>
+  <si>
     <t xml:space="preserve">Organisation Name</t>
   </si>
   <si>
@@ -46,18 +113,9 @@
     <t xml:space="preserve">Marvel</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
     <t xml:space="preserve">Department</t>
   </si>
   <si>
-    <t xml:space="preserve">Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile</t>
-  </si>
-  <si>
     <t xml:space="preserve">CON_002</t>
   </si>
   <si>
@@ -65,9 +123,6 @@
   </si>
   <si>
     <t xml:space="preserve">Avengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spiddy@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">Mailing City</t>
@@ -103,6 +158,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -124,6 +180,7 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -181,24 +238,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -325,16 +386,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -350,20 +405,34 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
@@ -373,37 +442,47 @@
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>7654345678</v>
-      </c>
+      <c r="E5" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>9654345678</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -413,48 +492,208 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E8" r:id="rId1" display="spiddy@gmail.com"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="18.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="17.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="14.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="18.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>7654345678</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>7687344685</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>22</v>
+      <c r="F8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
